--- a/app/src/main/assets/Pipistrelli 2022.xlsx
+++ b/app/src/main/assets/Pipistrelli 2022.xlsx
@@ -629,7 +629,11 @@
           <t>Sarcedo</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>45.7104304</v>
       </c>
@@ -801,7 +805,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>45.6577546</v>
       </c>

--- a/app/src/main/assets/Pipistrelli 2022.xlsx
+++ b/app/src/main/assets/Pipistrelli 2022.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torri di Quartesolo</t>
+          <t>Torri di quartesolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/app/src/main/assets/Pipistrelli 2022.xlsx
+++ b/app/src/main/assets/Pipistrelli 2022.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torri di quartesolo</t>
+          <t>Torri Di Quartesolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/app/src/main/assets/Pipistrelli 2022.xlsx
+++ b/app/src/main/assets/Pipistrelli 2022.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,6 +506,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Viale Margherita, 35</t>
@@ -522,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.5481426</v>
+        <v>45.54486</v>
       </c>
       <c r="I2" t="n">
-        <v>11.5548004</v>
+        <v>11.5516</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -545,9 +546,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44745</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,6 +562,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Via Brescia</t>
@@ -599,9 +602,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44754</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -614,6 +618,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Via San Giorgio</t>
@@ -653,9 +658,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44746</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,9 +718,10 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44747</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -771,9 +778,10 @@
           <t>liberato</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44858</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -786,6 +794,7 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Via Porto</t>
@@ -825,6 +834,7 @@
           <t>morto</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
